--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-02-2026.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.67</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>£40.05</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£35.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-pl4000-thermal-laminate-insulation-board?variant=55597627441536 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.tradeinsulations.co.uk/product/140mm-celotex-thermaclass/</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
